--- a/data/trans_dic/P36B13_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36B13_R-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,25%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>22,35; 31,33</t>
+          <t>22,26; 31,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 19,67</t>
+          <t>8,65; 19,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,65; 24,66</t>
+          <t>16,53; 24,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,95; 15,9</t>
+          <t>7,62; 16,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>20,84; 26,76</t>
+          <t>21,15; 27,13</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,54; 15,85</t>
+          <t>9,11; 16,42</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,83%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,84; 25,55</t>
+          <t>18,73; 25,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,92; 19,04</t>
+          <t>10,51; 19,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,34; 14,66</t>
+          <t>9,5; 14,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 5,57</t>
+          <t>1,99; 5,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,16; 19,65</t>
+          <t>14,94; 19,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 10,96</t>
+          <t>6,58; 11,38</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,43; 14,5</t>
+          <t>9,63; 14,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 10,36</t>
+          <t>5,54; 9,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,11; 10,46</t>
+          <t>6,24; 10,39</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,89</t>
+          <t>3,95; 7,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>8,4; 11,71</t>
+          <t>8,27; 11,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,15; 8,12</t>
+          <t>5,16; 7,99</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,65; 10,14</t>
+          <t>5,95; 10,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 71,36</t>
+          <t>5,21; 9,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,5; 7,06</t>
+          <t>3,65; 6,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,5; 4,68</t>
+          <t>2,66; 4,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,14; 7,98</t>
+          <t>5,21; 7,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,45; 49,74</t>
+          <t>4,39; 6,63</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,06%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,43; 7,75</t>
+          <t>3,45; 7,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,93</t>
+          <t>3,05; 6,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,94</t>
+          <t>2,87; 6,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 2,61</t>
+          <t>0,92; 2,73</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,55; 6,58</t>
+          <t>3,56; 6,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,07; 3,95</t>
+          <t>2,22; 4,15</t>
         </is>
       </c>
     </row>
@@ -999,27 +999,27 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3,37%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3,04%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,14</t>
+          <t>2,07; 6,04</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,15; 5,21</t>
+          <t>2,08; 5,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 5,26</t>
+          <t>1,62; 5,1</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,8</t>
+          <t>0,8; 2,63</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,89</t>
+          <t>2,26; 5,07</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,77</t>
+          <t>1,6; 3,39</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 6,44</t>
+          <t>1,87; 6,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,72; 3,26</t>
+          <t>0,7; 3,35</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,55</t>
+          <t>1,01; 4,65</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,24</t>
+          <t>1,17; 3,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,28</t>
+          <t>1,74; 4,55</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,73</t>
+          <t>1,22; 2,97</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>11,38; 13,65</t>
+          <t>11,42; 13,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6,95; 35,52</t>
+          <t>6,42; 8,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,03; 8,81</t>
+          <t>7,01; 8,73</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,74; 4,13</t>
+          <t>3,25; 4,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>9,45; 10,86</t>
+          <t>9,39; 10,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,01; 19,71</t>
+          <t>5,02; 6,34</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>51100</t>
+          <t>53376</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33629</t>
+          <t>40791</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84729</t>
+          <t>94168</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>93768; 131431</t>
+          <t>93359; 131317</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32726; 78687</t>
+          <t>35289; 78203</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>65719; 97360</t>
+          <t>65259; 96296</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21654; 49532</t>
+          <t>27504; 60441</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>169671; 217874</t>
+          <t>172251; 220897</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>60805; 112770</t>
+          <t>70026; 126203</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>60017</t>
+          <t>68875</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>17522</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77148</t>
+          <t>86398</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>111071; 150647</t>
+          <t>110441; 151480</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>42018; 80646</t>
+          <t>50113; 91784</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>52568; 82500</t>
+          <t>53462; 82357</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8328; 28507</t>
+          <t>9985; 29164</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>174729; 226437</t>
+          <t>172201; 224701</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53496; 102448</t>
+          <t>64377; 111266</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>41336</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69503</t>
+          <t>79610</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62751; 96499</t>
+          <t>64086; 97697</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>30221; 55572</t>
+          <t>34385; 61483</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>40258; 68874</t>
+          <t>41112; 68383</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20422; 37264</t>
+          <t>24485; 43791</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>111213; 155063</t>
+          <t>109479; 154787</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>55439; 87505</t>
+          <t>64109; 99141</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>284819</t>
+          <t>49032</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24909</t>
+          <t>27388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>309728</t>
+          <t>76420</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36429; 65372</t>
+          <t>38369; 65963</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>49788; 632159</t>
+          <t>36416; 66665</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22607; 45588</t>
+          <t>23570; 44736</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17742; 33210</t>
+          <t>19524; 36156</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66313; 103011</t>
+          <t>67213; 102160</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>70955; 793302</t>
+          <t>62810; 94866</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23022</t>
+          <t>27452</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31832</t>
+          <t>37102</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>16116; 36471</t>
+          <t>16219; 36541</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>15115; 33158</t>
+          <t>18548; 38836</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>14188; 34388</t>
+          <t>14207; 33893</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5297; 14224</t>
+          <t>5571; 16559</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>34271; 63585</t>
+          <t>34429; 61918</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>22935; 43648</t>
+          <t>26969; 50450</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>12409</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>6501</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>17944</t>
+          <t>20050</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6615; 20413</t>
+          <t>6891; 20062</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>7932; 19169</t>
+          <t>8476; 20755</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>6202; 19770</t>
+          <t>6082; 19149</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1685; 10948</t>
+          <t>3521; 11529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>15724; 34600</t>
+          <t>16007; 35928</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9688; 27015</t>
+          <t>13557; 28698</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>4557</t>
+          <t>5086</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8137</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>12695</t>
+          <t>14406</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>4414; 16204</t>
+          <t>4703; 16516</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2021; 9207</t>
+          <t>2171; 10374</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3799; 17674</t>
+          <t>3919; 18029</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>4789; 13796</t>
+          <t>5439; 16023</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>10505; 27406</t>
+          <t>11100; 29130</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8000; 19301</t>
+          <t>9442; 22986</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>477261</t>
+          <t>263777</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>126318</t>
+          <t>144376</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>603580</t>
+          <t>408153</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>383818; 460533</t>
+          <t>385296; 460979</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>240232; 1227438</t>
+          <t>226688; 307138</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>247534; 310290</t>
+          <t>246674; 307483</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>100023; 150946</t>
+          <t>121123; 169961</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>651834; 748461</t>
+          <t>647309; 745995</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>356457; 1400988</t>
+          <t>364422; 459804</t>
         </is>
       </c>
     </row>
